--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task055.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task055.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -295,6 +295,50 @@
         <v>7.2635775276947969</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>304</v>
+      </c>
+      <c r="B5" s="0">
+        <v>220</v>
+      </c>
+      <c r="C5" s="0">
+        <v>304</v>
+      </c>
+      <c r="D5" s="0">
+        <v>88.347688019732189</v>
+      </c>
+      <c r="E5" s="0">
+        <v>441.42000000000002</v>
+      </c>
+      <c r="F5" s="0">
+        <v>166.85150689487762</v>
+      </c>
+      <c r="G5" s="0">
+        <v>28207.758792304463</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-8301.8905910274552</v>
+      </c>
+      <c r="I5" s="0">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="J5" s="0">
+        <v>10.195</v>
+      </c>
+      <c r="K5" s="0">
+        <v>1.6399999999999997</v>
+      </c>
+      <c r="L5" s="0">
+        <v>2.415</v>
+      </c>
+      <c r="M5" s="0">
+        <v>300.07294671342032</v>
+      </c>
+      <c r="N5" s="0">
+        <v>7.2635775276947969</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>